--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -2079,45 +2079,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130873731</v>
+        <v>130873694</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438582</v>
+        <v>438770</v>
       </c>
       <c r="R16" t="n">
-        <v>6795186</v>
+        <v>6795130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,53 +2184,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130873694</v>
+        <v>130873731</v>
       </c>
       <c r="B17" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438770</v>
+        <v>438582</v>
       </c>
       <c r="R17" t="n">
-        <v>6795130</v>
+        <v>6795186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2572,45 +2572,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130873726</v>
+        <v>130873699</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>57056</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438662</v>
+        <v>438808</v>
       </c>
       <c r="R21" t="n">
-        <v>6795157</v>
+        <v>6795184</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,53 +2677,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130873699</v>
+        <v>130873726</v>
       </c>
       <c r="B22" t="n">
-        <v>57056</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438808</v>
+        <v>438662</v>
       </c>
       <c r="R22" t="n">
-        <v>6795184</v>
+        <v>6795157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3974,43 +3974,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130873703</v>
+        <v>130873697</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>91797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4018,10 +4012,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439003</v>
+        <v>438905</v>
       </c>
       <c r="R35" t="n">
-        <v>6795150</v>
+        <v>6795075</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4074,44 +4068,50 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130873697</v>
+        <v>130873703</v>
       </c>
       <c r="B36" t="n">
-        <v>91797</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438905</v>
+        <v>439003</v>
       </c>
       <c r="R36" t="n">
-        <v>6795075</v>
+        <v>6795150</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -1089,45 +1089,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130873722</v>
+        <v>130873693</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438858</v>
+        <v>438755</v>
       </c>
       <c r="R6" t="n">
-        <v>6795118</v>
+        <v>6795183</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130873728</v>
+        <v>130873722</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1221,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438641</v>
+        <v>438858</v>
       </c>
       <c r="R7" t="n">
-        <v>6795153</v>
+        <v>6795118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130873733</v>
+        <v>130873728</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1318,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438651</v>
+        <v>438641</v>
       </c>
       <c r="R8" t="n">
-        <v>6795214</v>
+        <v>6795153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,7 +1388,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130873741</v>
+        <v>130873733</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1415,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438767</v>
+        <v>438651</v>
       </c>
       <c r="R9" t="n">
-        <v>6795135</v>
+        <v>6795214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,53 +1586,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130873693</v>
+        <v>130873741</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438755</v>
+        <v>438767</v>
       </c>
       <c r="R11" t="n">
-        <v>6795183</v>
+        <v>6795135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2079,53 +2079,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130873694</v>
+        <v>130873731</v>
       </c>
       <c r="B16" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438770</v>
+        <v>438582</v>
       </c>
       <c r="R16" t="n">
-        <v>6795130</v>
+        <v>6795186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,45 +2176,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130873731</v>
+        <v>130873694</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438582</v>
+        <v>438770</v>
       </c>
       <c r="R17" t="n">
-        <v>6795186</v>
+        <v>6795130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3269,40 +3269,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130873698</v>
+        <v>130873701</v>
       </c>
       <c r="B28" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3312,10 +3313,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438966</v>
+        <v>438757</v>
       </c>
       <c r="R28" t="n">
-        <v>6795127</v>
+        <v>6795166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,6 +3357,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3374,41 +3376,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130873701</v>
+        <v>130873698</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3418,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438757</v>
+        <v>438966</v>
       </c>
       <c r="R29" t="n">
-        <v>6795166</v>
+        <v>6795127</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,7 +3463,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130873742</v>
+        <v>130873697</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>91797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3791,34 +3791,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438980</v>
+        <v>438905</v>
       </c>
       <c r="R33" t="n">
-        <v>6795131</v>
+        <v>6795075</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,6 +3862,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3870,14 +3874,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130873727</v>
+        <v>130873742</v>
       </c>
       <c r="B34" t="n">
         <v>79221</v>
@@ -3912,10 +3916,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438675</v>
+        <v>438980</v>
       </c>
       <c r="R34" t="n">
-        <v>6795125</v>
+        <v>6795131</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,10 +3978,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130873697</v>
+        <v>130873727</v>
       </c>
       <c r="B35" t="n">
-        <v>91797</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,37 +3989,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438905</v>
+        <v>438675</v>
       </c>
       <c r="R35" t="n">
-        <v>6795075</v>
+        <v>6795125</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4056,7 +4057,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130873729</v>
+        <v>130873736</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4211,16 +4211,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438627</v>
+        <v>438769</v>
       </c>
       <c r="R37" t="n">
-        <v>6795176</v>
+        <v>6795216</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4261,6 +4264,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4279,7 +4283,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130873736</v>
+        <v>130873729</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4308,19 +4312,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438769</v>
+        <v>438627</v>
       </c>
       <c r="R38" t="n">
-        <v>6795216</v>
+        <v>6795176</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4361,7 +4362,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -1089,53 +1089,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130873693</v>
+        <v>130873722</v>
       </c>
       <c r="B6" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438755</v>
+        <v>438858</v>
       </c>
       <c r="R6" t="n">
-        <v>6795183</v>
+        <v>6795118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130873722</v>
+        <v>130873728</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1229,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438858</v>
+        <v>438641</v>
       </c>
       <c r="R7" t="n">
-        <v>6795118</v>
+        <v>6795153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1283,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130873728</v>
+        <v>130873733</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1326,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438641</v>
+        <v>438651</v>
       </c>
       <c r="R8" t="n">
-        <v>6795153</v>
+        <v>6795214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130873733</v>
+        <v>130873730</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1417,16 +1409,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438651</v>
+        <v>438606</v>
       </c>
       <c r="R9" t="n">
-        <v>6795214</v>
+        <v>6795190</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1485,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130873730</v>
+        <v>130873741</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1514,19 +1510,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438606</v>
+        <v>438767</v>
       </c>
       <c r="R10" t="n">
-        <v>6795190</v>
+        <v>6795135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1586,45 +1578,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130873741</v>
+        <v>130873693</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438767</v>
+        <v>438755</v>
       </c>
       <c r="R11" t="n">
-        <v>6795135</v>
+        <v>6795183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130873721</v>
+        <v>130873707</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>56436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,34 +1888,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438889</v>
+        <v>438781</v>
       </c>
       <c r="R14" t="n">
-        <v>6795083</v>
+        <v>6795138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,17 +1975,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130873707</v>
+        <v>130873721</v>
       </c>
       <c r="B15" t="n">
-        <v>56436</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1985,42 +1993,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438781</v>
+        <v>438889</v>
       </c>
       <c r="R15" t="n">
-        <v>6795138</v>
+        <v>6795083</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2572,53 +2572,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130873699</v>
+        <v>130873726</v>
       </c>
       <c r="B21" t="n">
-        <v>57056</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438808</v>
+        <v>438662</v>
       </c>
       <c r="R21" t="n">
-        <v>6795184</v>
+        <v>6795157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2677,45 +2669,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130873726</v>
+        <v>130873699</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>57056</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438662</v>
+        <v>438808</v>
       </c>
       <c r="R22" t="n">
-        <v>6795157</v>
+        <v>6795184</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3269,41 +3269,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130873701</v>
+        <v>130873698</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3313,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438757</v>
+        <v>438966</v>
       </c>
       <c r="R28" t="n">
-        <v>6795166</v>
+        <v>6795127</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,7 +3356,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3376,40 +3374,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130873698</v>
+        <v>130873701</v>
       </c>
       <c r="B29" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3419,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438966</v>
+        <v>438757</v>
       </c>
       <c r="R29" t="n">
-        <v>6795127</v>
+        <v>6795166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3463,6 +3462,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3481,45 +3481,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130873720</v>
+        <v>130873695</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438986</v>
+        <v>438796</v>
       </c>
       <c r="R30" t="n">
-        <v>6795080</v>
+        <v>6795140</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3578,7 +3586,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130873734</v>
+        <v>130873720</v>
       </c>
       <c r="B31" t="n">
         <v>79221</v>
@@ -3613,10 +3621,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438769</v>
+        <v>438986</v>
       </c>
       <c r="R31" t="n">
-        <v>6795253</v>
+        <v>6795080</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,53 +3683,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130873695</v>
+        <v>130873734</v>
       </c>
       <c r="B32" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438796</v>
+        <v>438769</v>
       </c>
       <c r="R32" t="n">
-        <v>6795140</v>
+        <v>6795253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -1089,45 +1089,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130873722</v>
+        <v>130873693</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438858</v>
+        <v>438755</v>
       </c>
       <c r="R6" t="n">
-        <v>6795118</v>
+        <v>6795183</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130873728</v>
+        <v>130873722</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1221,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438641</v>
+        <v>438858</v>
       </c>
       <c r="R7" t="n">
-        <v>6795153</v>
+        <v>6795118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130873733</v>
+        <v>130873728</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1318,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438651</v>
+        <v>438641</v>
       </c>
       <c r="R8" t="n">
-        <v>6795214</v>
+        <v>6795153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,7 +1388,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130873730</v>
+        <v>130873733</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1409,19 +1417,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438606</v>
+        <v>438651</v>
       </c>
       <c r="R9" t="n">
-        <v>6795190</v>
+        <v>6795214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1467,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,7 +1485,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130873741</v>
+        <v>130873730</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1510,16 +1514,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438767</v>
+        <v>438606</v>
       </c>
       <c r="R10" t="n">
-        <v>6795135</v>
+        <v>6795190</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,6 +1567,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,53 +1586,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130873693</v>
+        <v>130873741</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438755</v>
+        <v>438767</v>
       </c>
       <c r="R11" t="n">
-        <v>6795183</v>
+        <v>6795135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130873707</v>
+        <v>130873721</v>
       </c>
       <c r="B14" t="n">
-        <v>56436</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,42 +1888,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438781</v>
+        <v>438889</v>
       </c>
       <c r="R14" t="n">
-        <v>6795138</v>
+        <v>6795083</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,17 +1967,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130873721</v>
+        <v>130873707</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>56436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,34 +1985,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438889</v>
+        <v>438781</v>
       </c>
       <c r="R15" t="n">
-        <v>6795083</v>
+        <v>6795138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
         <v>130873719</v>
       </c>
       <c r="B20" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3269,40 +3269,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130873698</v>
+        <v>130873701</v>
       </c>
       <c r="B28" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3312,10 +3313,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438966</v>
+        <v>438757</v>
       </c>
       <c r="R28" t="n">
-        <v>6795127</v>
+        <v>6795166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,6 +3357,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3374,41 +3376,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130873701</v>
+        <v>130873698</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3418,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438757</v>
+        <v>438966</v>
       </c>
       <c r="R29" t="n">
-        <v>6795166</v>
+        <v>6795127</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,7 +3463,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3780,37 +3780,43 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130873697</v>
+        <v>130873703</v>
       </c>
       <c r="B33" t="n">
-        <v>91797</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3818,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438905</v>
+        <v>439003</v>
       </c>
       <c r="R33" t="n">
-        <v>6795075</v>
+        <v>6795150</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3874,7 +3880,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4075,43 +4081,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130873703</v>
+        <v>130873697</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>91805</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439003</v>
+        <v>438905</v>
       </c>
       <c r="R36" t="n">
-        <v>6795150</v>
+        <v>6795075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -1089,53 +1089,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130873693</v>
+        <v>130873722</v>
       </c>
       <c r="B6" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438755</v>
+        <v>438858</v>
       </c>
       <c r="R6" t="n">
-        <v>6795183</v>
+        <v>6795118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130873722</v>
+        <v>130873728</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1229,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438858</v>
+        <v>438641</v>
       </c>
       <c r="R7" t="n">
-        <v>6795118</v>
+        <v>6795153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1283,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130873728</v>
+        <v>130873733</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1326,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438641</v>
+        <v>438651</v>
       </c>
       <c r="R8" t="n">
-        <v>6795153</v>
+        <v>6795214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130873733</v>
+        <v>130873730</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1417,16 +1409,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438651</v>
+        <v>438606</v>
       </c>
       <c r="R9" t="n">
-        <v>6795214</v>
+        <v>6795190</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1485,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130873730</v>
+        <v>130873741</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1514,19 +1510,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438606</v>
+        <v>438767</v>
       </c>
       <c r="R10" t="n">
-        <v>6795190</v>
+        <v>6795135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1586,45 +1578,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130873741</v>
+        <v>130873693</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438767</v>
+        <v>438755</v>
       </c>
       <c r="R11" t="n">
-        <v>6795135</v>
+        <v>6795183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130873721</v>
+        <v>130873707</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>56436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,34 +1888,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438889</v>
+        <v>438781</v>
       </c>
       <c r="R14" t="n">
-        <v>6795083</v>
+        <v>6795138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,17 +1975,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130873707</v>
+        <v>130873721</v>
       </c>
       <c r="B15" t="n">
-        <v>56436</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1985,42 +1993,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438781</v>
+        <v>438889</v>
       </c>
       <c r="R15" t="n">
-        <v>6795138</v>
+        <v>6795083</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,52 +2072,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130873731</v>
+        <v>130873694</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438582</v>
+        <v>438770</v>
       </c>
       <c r="R16" t="n">
-        <v>6795186</v>
+        <v>6795130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,53 +2184,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130873694</v>
+        <v>130873731</v>
       </c>
       <c r="B17" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438770</v>
+        <v>438582</v>
       </c>
       <c r="R17" t="n">
-        <v>6795130</v>
+        <v>6795186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130873732</v>
+        <v>130873719</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>91804</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,34 +2292,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438571</v>
+        <v>438646</v>
       </c>
       <c r="R18" t="n">
-        <v>6795200</v>
+        <v>6795245</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,6 +2359,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130873723</v>
+        <v>130873732</v>
       </c>
       <c r="B19" t="n">
         <v>79221</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438879</v>
+        <v>438571</v>
       </c>
       <c r="R19" t="n">
-        <v>6795213</v>
+        <v>6795200</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130873719</v>
+        <v>130873723</v>
       </c>
       <c r="B20" t="n">
-        <v>91804</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2486,33 +2486,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438646</v>
+        <v>438879</v>
       </c>
       <c r="R20" t="n">
-        <v>6795245</v>
+        <v>6795213</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2553,7 +2554,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3269,41 +3269,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130873701</v>
+        <v>130873698</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3313,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438757</v>
+        <v>438966</v>
       </c>
       <c r="R28" t="n">
-        <v>6795166</v>
+        <v>6795127</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,7 +3356,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3376,40 +3374,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130873698</v>
+        <v>130873701</v>
       </c>
       <c r="B29" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3419,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438966</v>
+        <v>438757</v>
       </c>
       <c r="R29" t="n">
-        <v>6795127</v>
+        <v>6795166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3463,6 +3462,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3481,53 +3481,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130873695</v>
+        <v>130873720</v>
       </c>
       <c r="B30" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438796</v>
+        <v>438986</v>
       </c>
       <c r="R30" t="n">
-        <v>6795140</v>
+        <v>6795080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3586,7 +3578,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130873720</v>
+        <v>130873734</v>
       </c>
       <c r="B31" t="n">
         <v>79221</v>
@@ -3621,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438986</v>
+        <v>438769</v>
       </c>
       <c r="R31" t="n">
-        <v>6795080</v>
+        <v>6795253</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,45 +3675,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130873734</v>
+        <v>130873695</v>
       </c>
       <c r="B32" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438769</v>
+        <v>438796</v>
       </c>
       <c r="R32" t="n">
-        <v>6795253</v>
+        <v>6795140</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,43 +3780,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130873703</v>
+        <v>130873697</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>91805</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3824,10 +3818,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439003</v>
+        <v>438905</v>
       </c>
       <c r="R33" t="n">
-        <v>6795150</v>
+        <v>6795075</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3880,7 +3874,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4081,37 +4075,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130873697</v>
+        <v>130873703</v>
       </c>
       <c r="B36" t="n">
-        <v>91805</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438905</v>
+        <v>439003</v>
       </c>
       <c r="R36" t="n">
-        <v>6795075</v>
+        <v>6795150</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -887,45 +887,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130873745</v>
+        <v>130873700</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>57076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438633</v>
+        <v>438768</v>
       </c>
       <c r="R4" t="n">
-        <v>6795187</v>
+        <v>6795206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,60 +985,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130873700</v>
+        <v>130873745</v>
       </c>
       <c r="B5" t="n">
-        <v>57076</v>
+        <v>79244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438768</v>
+        <v>438633</v>
       </c>
       <c r="R5" t="n">
-        <v>6795206</v>
+        <v>6795187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,60 +1082,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130873693</v>
+        <v>130873722</v>
       </c>
       <c r="B6" t="n">
-        <v>57073</v>
+        <v>79244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438755</v>
+        <v>438858</v>
       </c>
       <c r="R6" t="n">
-        <v>6795183</v>
+        <v>6795118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130873730</v>
+        <v>130873728</v>
       </c>
       <c r="B7" t="n">
         <v>79244</v>
@@ -1223,19 +1215,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438606</v>
+        <v>438641</v>
       </c>
       <c r="R7" t="n">
-        <v>6795190</v>
+        <v>6795153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1265,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1392,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130873728</v>
+        <v>130873730</v>
       </c>
       <c r="B9" t="n">
         <v>79244</v>
@@ -1421,16 +1409,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438641</v>
+        <v>438606</v>
       </c>
       <c r="R9" t="n">
-        <v>6795153</v>
+        <v>6795190</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1489,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130873722</v>
+        <v>130873741</v>
       </c>
       <c r="B10" t="n">
         <v>79244</v>
@@ -1524,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438858</v>
+        <v>438767</v>
       </c>
       <c r="R10" t="n">
-        <v>6795118</v>
+        <v>6795135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,45 +1578,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130873741</v>
+        <v>130873693</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>57073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438767</v>
+        <v>438755</v>
       </c>
       <c r="R11" t="n">
-        <v>6795135</v>
+        <v>6795183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130873732</v>
+        <v>130873719</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2389,34 +2389,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438571</v>
+        <v>438646</v>
       </c>
       <c r="R19" t="n">
-        <v>6795200</v>
+        <v>6795245</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2457,6 +2456,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2468,17 +2468,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130873719</v>
+        <v>130873732</v>
       </c>
       <c r="B20" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2486,33 +2486,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438646</v>
+        <v>438571</v>
       </c>
       <c r="R20" t="n">
-        <v>6795245</v>
+        <v>6795200</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2553,7 +2554,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2565,60 +2565,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130873699</v>
+        <v>130873726</v>
       </c>
       <c r="B21" t="n">
-        <v>57076</v>
+        <v>79244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438808</v>
+        <v>438662</v>
       </c>
       <c r="R21" t="n">
-        <v>6795184</v>
+        <v>6795157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2677,45 +2669,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130873726</v>
+        <v>130873699</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>57076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438662</v>
+        <v>438808</v>
       </c>
       <c r="R22" t="n">
-        <v>6795157</v>
+        <v>6795184</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130873724</v>
+        <v>130873735</v>
       </c>
       <c r="B24" t="n">
         <v>79244</v>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438724</v>
+        <v>438776</v>
       </c>
       <c r="R24" t="n">
-        <v>6795185</v>
+        <v>6795246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2968,7 +2968,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130873735</v>
+        <v>130873724</v>
       </c>
       <c r="B25" t="n">
         <v>79244</v>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438776</v>
+        <v>438724</v>
       </c>
       <c r="R25" t="n">
-        <v>6795246</v>
+        <v>6795185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3269,41 +3269,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130873701</v>
+        <v>130873698</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3313,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438757</v>
+        <v>438966</v>
       </c>
       <c r="R28" t="n">
-        <v>6795166</v>
+        <v>6795127</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,7 +3356,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3376,40 +3374,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130873698</v>
+        <v>130873701</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3419,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438966</v>
+        <v>438757</v>
       </c>
       <c r="R29" t="n">
-        <v>6795127</v>
+        <v>6795166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3463,6 +3462,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3481,45 +3481,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130873734</v>
+        <v>130873695</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>57073</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438769</v>
+        <v>438796</v>
       </c>
       <c r="R30" t="n">
-        <v>6795253</v>
+        <v>6795140</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3675,53 +3683,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130873695</v>
+        <v>130873734</v>
       </c>
       <c r="B32" t="n">
-        <v>57073</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438796</v>
+        <v>438769</v>
       </c>
       <c r="R32" t="n">
-        <v>6795140</v>
+        <v>6795253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130873697</v>
+        <v>130873742</v>
       </c>
       <c r="B33" t="n">
-        <v>91830</v>
+        <v>79244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3791,37 +3791,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438905</v>
+        <v>438980</v>
       </c>
       <c r="R33" t="n">
-        <v>6795075</v>
+        <v>6795131</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,7 +3859,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3874,17 +3870,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130873742</v>
+        <v>130873697</v>
       </c>
       <c r="B34" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,34 +3888,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438980</v>
+        <v>438905</v>
       </c>
       <c r="R34" t="n">
-        <v>6795131</v>
+        <v>6795075</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3960,6 +3959,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -887,53 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130873700</v>
+        <v>130873745</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>79244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438768</v>
+        <v>438633</v>
       </c>
       <c r="R4" t="n">
-        <v>6795206</v>
+        <v>6795187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,52 +977,60 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130873745</v>
+        <v>130873700</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>57076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438633</v>
+        <v>438768</v>
       </c>
       <c r="R5" t="n">
-        <v>6795187</v>
+        <v>6795206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2079,45 +2079,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130873731</v>
+        <v>130873694</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>57073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438582</v>
+        <v>438770</v>
       </c>
       <c r="R16" t="n">
-        <v>6795186</v>
+        <v>6795130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,53 +2184,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130873694</v>
+        <v>130873731</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>79244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438770</v>
+        <v>438582</v>
       </c>
       <c r="R17" t="n">
-        <v>6795130</v>
+        <v>6795186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130873719</v>
+        <v>130873732</v>
       </c>
       <c r="B19" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2389,33 +2389,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438646</v>
+        <v>438571</v>
       </c>
       <c r="R19" t="n">
-        <v>6795245</v>
+        <v>6795200</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,7 +2457,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2468,17 +2468,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130873732</v>
+        <v>130873719</v>
       </c>
       <c r="B20" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2486,34 +2486,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438571</v>
+        <v>438646</v>
       </c>
       <c r="R20" t="n">
-        <v>6795200</v>
+        <v>6795245</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2554,6 +2553,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2871,45 +2871,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130873735</v>
+        <v>130873702</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438776</v>
+        <v>438985</v>
       </c>
       <c r="R24" t="n">
-        <v>6795246</v>
+        <v>6795128</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,6 +2959,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3065,54 +3075,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130873702</v>
+        <v>130873735</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438985</v>
+        <v>438776</v>
       </c>
       <c r="R26" t="n">
-        <v>6795128</v>
+        <v>6795246</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,7 +3154,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3269,40 +3269,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130873698</v>
+        <v>130873701</v>
       </c>
       <c r="B28" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3312,10 +3313,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438966</v>
+        <v>438757</v>
       </c>
       <c r="R28" t="n">
-        <v>6795127</v>
+        <v>6795166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,6 +3357,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3374,41 +3376,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130873701</v>
+        <v>130873698</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3418,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438757</v>
+        <v>438966</v>
       </c>
       <c r="R29" t="n">
-        <v>6795166</v>
+        <v>6795127</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,7 +3463,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3481,53 +3481,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130873695</v>
+        <v>130873720</v>
       </c>
       <c r="B30" t="n">
-        <v>57073</v>
+        <v>79244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438796</v>
+        <v>438986</v>
       </c>
       <c r="R30" t="n">
-        <v>6795140</v>
+        <v>6795080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3586,7 +3578,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130873720</v>
+        <v>130873734</v>
       </c>
       <c r="B31" t="n">
         <v>79244</v>
@@ -3621,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438986</v>
+        <v>438769</v>
       </c>
       <c r="R31" t="n">
-        <v>6795080</v>
+        <v>6795253</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,45 +3675,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130873734</v>
+        <v>130873695</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>57073</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438769</v>
+        <v>438796</v>
       </c>
       <c r="R32" t="n">
-        <v>6795253</v>
+        <v>6795140</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130873742</v>
+        <v>130873727</v>
       </c>
       <c r="B33" t="n">
         <v>79244</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438980</v>
+        <v>438675</v>
       </c>
       <c r="R33" t="n">
-        <v>6795131</v>
+        <v>6795125</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3877,37 +3877,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130873697</v>
+        <v>130873703</v>
       </c>
       <c r="B34" t="n">
-        <v>91830</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3915,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438905</v>
+        <v>439003</v>
       </c>
       <c r="R34" t="n">
-        <v>6795075</v>
+        <v>6795150</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3971,17 +3977,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130873727</v>
+        <v>130873697</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3989,34 +3995,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438675</v>
+        <v>438905</v>
       </c>
       <c r="R35" t="n">
-        <v>6795125</v>
+        <v>6795075</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4057,6 +4066,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4068,61 +4078,52 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130873703</v>
+        <v>130873742</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439003</v>
+        <v>438980</v>
       </c>
       <c r="R36" t="n">
-        <v>6795150</v>
+        <v>6795131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,7 +4164,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130873736</v>
+        <v>130873729</v>
       </c>
       <c r="B37" t="n">
         <v>79244</v>
@@ -4211,19 +4211,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438769</v>
+        <v>438627</v>
       </c>
       <c r="R37" t="n">
-        <v>6795216</v>
+        <v>6795176</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,7 +4261,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4283,7 +4279,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130873729</v>
+        <v>130873736</v>
       </c>
       <c r="B38" t="n">
         <v>79244</v>
@@ -4312,16 +4308,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Snipan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438627</v>
+        <v>438769</v>
       </c>
       <c r="R38" t="n">
-        <v>6795176</v>
+        <v>6795216</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,6 +4361,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61999-2025 artfynd.xlsx
+++ b/artfynd/A 61999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873697</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873721</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873722</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873723</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873724</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873725</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873726</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873727</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873728</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873729</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873730</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873731</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873732</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873733</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873734</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873735</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873736</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873737</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873739</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2721,6 +2826,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873740</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2818,6 +2928,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873741</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873742</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3012,6 +3132,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873743</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873745</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3214,6 +3344,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873698</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58631</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3416,6 +3556,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873693</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3521,6 +3666,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873694</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3626,6 +3776,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873695</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3731,6 +3886,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873699</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3836,6 +3996,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873700</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3941,6 +4106,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873705</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4048,6 +4218,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873701</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4155,6 +4330,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873702</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4262,6 +4442,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873703</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4369,6 +4554,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873748</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4474,8 +4664,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130873707</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>